--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486511_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486511_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1515</v>
+        <v>6.9473</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7755</v>
+        <v>4.6638</v>
       </c>
       <c r="F2" t="n">
-        <v>2.376</v>
+        <v>2.2835</v>
       </c>
       <c r="G2" t="n">
         <v>5.1217</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5548</v>
+        <v>0.3506</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1406</v>
+        <v>0.0288</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4142</v>
+        <v>0.3217</v>
       </c>
       <c r="V2" t="n">
         <v>-0.265</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8831</v>
+        <v>1.3551</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3883</v>
+        <v>1.8295</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5052</v>
+        <v>-0.4744</v>
       </c>
       <c r="G3" t="n">
         <v>0.5024</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8581</v>
+        <v>0.3302</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7487</v>
+        <v>0.1899</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1095</v>
+        <v>0.1403</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5649999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ROBERTS</t>
+          <t>P. SCRUBB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3626</v>
+        <v>1.3423</v>
       </c>
       <c r="E4" t="n">
-        <v>1.396</v>
+        <v>-0.3401</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0334</v>
+        <v>1.6824</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0252</v>
+        <v>-1.88</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8181</v>
+        <v>-1.405</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7929</v>
+        <v>-0.4749</v>
       </c>
       <c r="J4" t="n">
-        <v>1.062</v>
+        <v>-2.1222</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9855</v>
+        <v>-1.4536</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0765</v>
+        <v>-0.6686</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0368</v>
+        <v>0.2422</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1674</v>
+        <v>0.0486</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8694</v>
+        <v>0.1936</v>
       </c>
       <c r="P4" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9025</v>
+        <v>0.2445</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3341</v>
+        <v>-0.1081</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5684</v>
+        <v>0.3527</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SCRUBB</t>
+          <t>J. ROBERTS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2691</v>
+        <v>0.7191</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2284</v>
+        <v>1.0608</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4975</v>
+        <v>-0.3416</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.88</v>
+        <v>0.0252</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.405</v>
+        <v>0.8181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4749</v>
+        <v>-0.7929</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.1222</v>
+        <v>1.062</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4536</v>
+        <v>0.9855</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6686</v>
+        <v>0.0765</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2422</v>
+        <v>-1.0368</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0486</v>
+        <v>-0.1674</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1936</v>
+        <v>-0.8694</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1714</v>
+        <v>0.259</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0036</v>
+        <v>-0.0012</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1678</v>
+        <v>0.2602</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7356</v>
+        <v>0.4495</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5717</v>
+        <v>0.1932</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1639</v>
+        <v>0.2563</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6672</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5327</v>
+        <v>0.2466</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5312</v>
+        <v>0.1526</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0016</v>
+        <v>0.094</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2718</v>
+        <v>-2.5104</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2708</v>
+        <v>-2.8438</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.001</v>
+        <v>0.3334</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2366</v>
+        <v>-1.5194</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1125</v>
+        <v>-0.6141</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3492</v>
+        <v>-0.9053</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.062</v>
+        <v>-1.0388</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3134</v>
+        <v>-1.1918</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3754</v>
+        <v>0.153</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1747</v>
+        <v>-0.4806</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2009</v>
+        <v>0.5776</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9738</v>
+        <v>-1.0583</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2723</v>
+        <v>0.0141</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1214</v>
+        <v>-0.4326</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3937</v>
+        <v>0.4467</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.395</v>
+        <v>0.2999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.395</v>
+        <v>-1.5902</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3516</v>
+        <v>-2.6186</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0241</v>
+        <v>-2.4944</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6725</v>
+        <v>-0.1243</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5194</v>
+        <v>-2.2366</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6141</v>
+        <v>0.1125</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9053</v>
+        <v>-2.3492</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0388</v>
+        <v>-1.062</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1918</v>
+        <v>0.3134</v>
       </c>
       <c r="L8" t="n">
-        <v>0.153</v>
+        <v>-1.3754</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4806</v>
+        <v>-1.1747</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5776</v>
+        <v>-0.2009</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0583</v>
+        <v>-0.9738</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1729</v>
+        <v>-0.0745</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6128</v>
+        <v>-0.3449</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.2704</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2999</v>
+        <v>-1.395</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5902</v>
+        <v>-1.395</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4654</v>
+        <v>-2.7572</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8837</v>
+        <v>-0.1446</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5818</v>
+        <v>-2.6126</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2464</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9591</v>
+        <v>-0.2509</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0719</v>
+        <v>-0.3329</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1128</v>
+        <v>0.082</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5649999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6545</v>
+        <v>-4.8115</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9012</v>
+        <v>-2.2739</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7533</v>
+        <v>-2.5376</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5078</v>
@@ -1234,13 +1234,13 @@
         <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6647</v>
+        <v>-0.8217</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1524</v>
+        <v>-0.5251</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5123</v>
+        <v>-0.2965</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5695</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7181</v>
+        <v>-5.8327</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0025</v>
+        <v>-5.487</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7156</v>
+        <v>-0.3457</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4046</v>
@@ -1312,13 +1312,13 @@
         <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5259</v>
+        <v>-0.6405</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2209</v>
+        <v>-0.7054</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.305</v>
+        <v>0.0649</v>
       </c>
       <c r="V11" t="n">
         <v>-0.83</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.059499999999998</v>
+        <v>-7.717099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.1792</v>
+        <v>-5.836500000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8804</v>
+        <v>-1.8806</v>
       </c>
       <c r="G12" t="n">
         <v>-9.812700000000001</v>
@@ -1390,13 +1390,13 @@
         <v>15.2255</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6849999999999998</v>
+        <v>-0.3425999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.421200000000001</v>
+        <v>-2.0789</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7365</v>
+        <v>1.7364</v>
       </c>
       <c r="V12" t="n">
         <v>-2.9994</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5603</v>
+        <v>6.8635</v>
       </c>
       <c r="E13" t="n">
         <v>4.8298</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7306</v>
+        <v>2.0337</v>
       </c>
       <c r="G13" t="n">
         <v>3.0937</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1833</v>
+        <v>0.1199</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4879</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3046</v>
+        <v>0.6077</v>
       </c>
       <c r="V13" t="n">
         <v>4.5199</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2463</v>
+        <v>6.7177</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0562</v>
+        <v>4.168</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1901</v>
+        <v>2.5498</v>
       </c>
       <c r="G14" t="n">
         <v>3.332</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1096</v>
+        <v>0.581</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1334</v>
+        <v>-0.0216</v>
       </c>
       <c r="U14" t="n">
-        <v>0.243</v>
+        <v>0.6026</v>
       </c>
       <c r="V14" t="n">
         <v>1.4997</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0915</v>
+        <v>4.0689</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1408</v>
+        <v>1.4761</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9506</v>
+        <v>2.5928</v>
       </c>
       <c r="G15" t="n">
         <v>4.4102</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3187</v>
+        <v>-0.3413</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0154</v>
+        <v>-0.6801</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3033</v>
+        <v>0.3389</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0456</v>
+        <v>2.1605</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0734</v>
+        <v>2.5205</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0279</v>
+        <v>-0.36</v>
       </c>
       <c r="G16" t="n">
         <v>2.0343</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1834</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3869</v>
+        <v>0.0601</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7965</v>
+        <v>-0.1286</v>
       </c>
       <c r="V16" t="n">
         <v>1.4997</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.905</v>
+        <v>0.842</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0681</v>
+        <v>0.7328</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1631</v>
+        <v>0.1092</v>
       </c>
       <c r="G17" t="n">
         <v>3.0213</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0137</v>
+        <v>-0.0493</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0721</v>
+        <v>-0.2632</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0584</v>
+        <v>0.2139</v>
       </c>
       <c r="V17" t="n">
         <v>-1.695</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. MC MULLEN</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1745</v>
+        <v>-0.9394</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4568</v>
+        <v>-0.4687</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2823</v>
+        <v>-0.4708</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9837</v>
+        <v>1.714</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1223</v>
+        <v>-0.9977</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8614000000000001</v>
+        <v>2.7117</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1595</v>
+        <v>2.5668</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7205</v>
+        <v>-0.3983</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4391</v>
+        <v>2.9651</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.8528</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4018</v>
+        <v>-0.5994</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4224</v>
+        <v>-0.2534</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8962</v>
+        <v>0.4993</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9648</v>
+        <v>0.2271</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9314</v>
+        <v>0.2722</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3045</v>
+        <v>-0.7602</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>N. MC MULLEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.978</v>
+        <v>-1.9047</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6922</v>
+        <v>-1.9097</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2858</v>
+        <v>0.0049</v>
       </c>
       <c r="G21" t="n">
-        <v>1.714</v>
+        <v>-1.9837</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9977</v>
+        <v>-1.1223</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7117</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5668</v>
+        <v>-1.1595</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3983</v>
+        <v>-0.7205</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9651</v>
+        <v>-0.4391</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8528</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5994</v>
+        <v>-0.4018</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2534</v>
+        <v>-0.4224</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3926</v>
+        <v>0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4607</v>
+        <v>1.1659</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0036</v>
+        <v>0.5119</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4571</v>
+        <v>0.654</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7602</v>
+        <v>-1.3045</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7621</v>
+        <v>-2.1384</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4105</v>
+        <v>-4.7458</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6484</v>
+        <v>2.6074</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7239</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5719</v>
+        <v>0.1956</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1334</v>
+        <v>-0.4687</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7053</v>
+        <v>0.6642</v>
       </c>
       <c r="V22" t="n">
         <v>0.5649999999999999</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3163</v>
+        <v>-2.3684</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8938</v>
+        <v>-1.2232</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4226</v>
+        <v>-1.1452</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7891</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8545</v>
+        <v>0.0934</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.0709</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1131</v>
+        <v>0.1643</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3252</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8683</v>
+        <v>-4.0621</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1973</v>
+        <v>-4.8621</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3291</v>
+        <v>0.8</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7431</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3098</v>
+        <v>0.116</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.4062</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0512</v>
+        <v>0.5221</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.0595</v>
+        <v>9.549599999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3806999999999992</v>
+        <v>0.3807</v>
       </c>
       <c r="F25" t="n">
-        <v>7.678699999999999</v>
+        <v>9.168800000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>9.8127</v>
+        <v>9.812700000000003</v>
       </c>
       <c r="H25" t="n">
         <v>1.6409</v>
@@ -2404,16 +2404,16 @@
         <v>9.7875</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6849999999999998</v>
+        <v>2.175</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.7363</v>
+        <v>-1.7365</v>
       </c>
       <c r="U25" t="n">
-        <v>2.4213</v>
+        <v>3.9113</v>
       </c>
       <c r="V25" t="n">
-        <v>2.999399999999999</v>
+        <v>2.999400000000001</v>
       </c>
       <c r="W25" t="n">
         <v>7.930499999999999</v>
